--- a/orecraft_database.xlsx
+++ b/orecraft_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB60AA33-07E1-413D-A30B-3142A00FDD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDDF852-D379-46B6-8A4C-ACC35E7FA4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,12 +23,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="82">
   <si>
     <t>type</t>
-  </si>
-  <si>
-    <t>naam</t>
-  </si>
-  <si>
-    <t>zeldzaamheid</t>
   </si>
   <si>
     <t>Copper Bar</t>
@@ -267,6 +261,12 @@
   <si>
     <t>Warlord Plate</t>
   </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
 </sst>
 </file>
 
@@ -414,10 +414,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -722,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:XFD73"/>
+  <dimension ref="A1:BX73"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -791,231 +791,231 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BR1" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BT1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AR1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="BO1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BP1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="BR1" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="BU1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="BV1" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="4">
@@ -1234,10 +1234,10 @@
     </row>
     <row r="3" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="8">
@@ -1456,10 +1456,10 @@
     </row>
     <row r="4" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="4">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="5" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="8">
@@ -1900,10 +1900,10 @@
     </row>
     <row r="6" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="5">
@@ -2122,10 +2122,10 @@
     </row>
     <row r="7" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="8">
@@ -2344,10 +2344,10 @@
     </row>
     <row r="8" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="5">
@@ -2566,10 +2566,10 @@
     </row>
     <row r="9" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="8">
@@ -2788,10 +2788,10 @@
     </row>
     <row r="10" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="5">
@@ -3010,10 +3010,10 @@
     </row>
     <row r="11" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="8">
@@ -3232,10 +3232,10 @@
     </row>
     <row r="12" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="5">
@@ -3454,10 +3454,10 @@
     </row>
     <row r="13" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="8">
@@ -3676,10 +3676,10 @@
     </row>
     <row r="14" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="5">
@@ -3898,10 +3898,10 @@
     </row>
     <row r="15" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="8">
@@ -4120,10 +4120,10 @@
     </row>
     <row r="16" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="5">
@@ -4342,10 +4342,10 @@
     </row>
     <row r="17" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="8">
@@ -4564,10 +4564,10 @@
     </row>
     <row r="18" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="5">
@@ -4786,10 +4786,10 @@
     </row>
     <row r="19" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="8">
@@ -5008,10 +5008,10 @@
     </row>
     <row r="20" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="5">
@@ -5230,10 +5230,10 @@
     </row>
     <row r="21" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="8">
@@ -5452,10 +5452,10 @@
     </row>
     <row r="22" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="5">
@@ -5674,10 +5674,10 @@
     </row>
     <row r="23" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="8">
@@ -5896,10 +5896,10 @@
     </row>
     <row r="24" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="5">
@@ -6118,10 +6118,10 @@
     </row>
     <row r="25" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="8">
@@ -6340,10 +6340,10 @@
     </row>
     <row r="26" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="5">
@@ -6562,10 +6562,10 @@
     </row>
     <row r="27" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="8">
@@ -6784,10 +6784,10 @@
     </row>
     <row r="28" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="5">
@@ -7006,10 +7006,10 @@
     </row>
     <row r="29" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="5">
@@ -7228,10 +7228,10 @@
     </row>
     <row r="30" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="5">
@@ -7448,12 +7448,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="5">
@@ -7670,12 +7670,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="5">
@@ -7892,12 +7892,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="8">
@@ -8114,12 +8114,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="5">
@@ -8336,12 +8336,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="8">
@@ -8558,12 +8558,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="5">
@@ -8780,12 +8780,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="8">
@@ -9002,12 +9002,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="5">
@@ -9224,12 +9224,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="8">
@@ -9446,12 +9446,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="4">
@@ -9668,12 +9668,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="8">
@@ -9890,12 +9890,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="5">
@@ -10112,12 +10112,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="8">
@@ -10334,12 +10334,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="5">
@@ -10556,12 +10556,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="8">
@@ -10778,12 +10778,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="5">
@@ -11000,12 +11000,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="8">
@@ -11222,12 +11222,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="5">
@@ -11444,12 +11444,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="8">
@@ -11666,12 +11666,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="5">
@@ -11888,12 +11888,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="8">
@@ -12110,12 +12110,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="8">
@@ -12332,12 +12332,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D53" s="8">
         <v>0</v>
@@ -12553,3823 +12553,3823 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" s="5">
+        <v>0</v>
+      </c>
+      <c r="E54" s="5">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5">
+        <v>0</v>
+      </c>
+      <c r="H54" s="5">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5">
+        <v>0</v>
+      </c>
+      <c r="J54" s="5">
+        <v>0</v>
+      </c>
+      <c r="K54" s="5">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5">
+        <v>0</v>
+      </c>
+      <c r="N54" s="5">
+        <v>0</v>
+      </c>
+      <c r="O54" s="5">
+        <v>0</v>
+      </c>
+      <c r="P54" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>0</v>
+      </c>
+      <c r="R54" s="5">
+        <v>0</v>
+      </c>
+      <c r="S54" s="5">
+        <v>0</v>
+      </c>
+      <c r="T54" s="5">
+        <v>0</v>
+      </c>
+      <c r="U54" s="5">
+        <v>0</v>
+      </c>
+      <c r="V54" s="5">
+        <v>0</v>
+      </c>
+      <c r="W54" s="5">
+        <v>0</v>
+      </c>
+      <c r="X54" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BC54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BD54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BE54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BF54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BG54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BI54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BJ54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BL54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BM54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BN54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BO54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BP54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BQ54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BR54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BS54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU54" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV54" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" s="8">
+        <v>0</v>
+      </c>
+      <c r="E55" s="8">
+        <v>0</v>
+      </c>
+      <c r="F55" s="8">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8">
+        <v>0</v>
+      </c>
+      <c r="H55" s="8">
+        <v>0</v>
+      </c>
+      <c r="I55" s="8">
+        <v>0</v>
+      </c>
+      <c r="J55" s="8">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8">
+        <v>0</v>
+      </c>
+      <c r="L55" s="8">
+        <v>0</v>
+      </c>
+      <c r="M55" s="8">
+        <v>0</v>
+      </c>
+      <c r="N55" s="8">
+        <v>0</v>
+      </c>
+      <c r="O55" s="8">
+        <v>0</v>
+      </c>
+      <c r="P55" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>0</v>
+      </c>
+      <c r="R55" s="8">
+        <v>0</v>
+      </c>
+      <c r="S55" s="8">
+        <v>0</v>
+      </c>
+      <c r="T55" s="8">
+        <v>0</v>
+      </c>
+      <c r="U55" s="8">
+        <v>0</v>
+      </c>
+      <c r="V55" s="8">
+        <v>0</v>
+      </c>
+      <c r="W55" s="5">
+        <v>0</v>
+      </c>
+      <c r="X55" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY55" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BG55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BH55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BJ55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BK55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BL55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BM55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BN55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BP55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BQ55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BR55" s="8">
+        <v>0</v>
+      </c>
+      <c r="BS55" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT55" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU55" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV55" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" s="5">
+        <v>0</v>
+      </c>
+      <c r="E56" s="5">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5">
+        <v>0</v>
+      </c>
+      <c r="H56" s="5">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5">
+        <v>0</v>
+      </c>
+      <c r="J56" s="5">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5">
+        <v>0</v>
+      </c>
+      <c r="M56" s="5">
+        <v>0</v>
+      </c>
+      <c r="N56" s="5">
+        <v>0</v>
+      </c>
+      <c r="O56" s="5">
+        <v>0</v>
+      </c>
+      <c r="P56" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="5">
+        <v>0</v>
+      </c>
+      <c r="R56" s="5">
+        <v>0</v>
+      </c>
+      <c r="S56" s="5">
+        <v>0</v>
+      </c>
+      <c r="T56" s="5">
+        <v>0</v>
+      </c>
+      <c r="U56" s="5">
+        <v>0</v>
+      </c>
+      <c r="V56" s="5">
+        <v>0</v>
+      </c>
+      <c r="W56" s="5">
+        <v>0</v>
+      </c>
+      <c r="X56" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BC56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BD56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BE56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BF56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BG56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BI56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BJ56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BL56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BM56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BN56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BO56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BP56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BQ56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BR56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BS56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU56" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV56" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" s="8">
+        <v>0</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0</v>
+      </c>
+      <c r="F57" s="8">
+        <v>0</v>
+      </c>
+      <c r="G57" s="8">
+        <v>0</v>
+      </c>
+      <c r="H57" s="8">
+        <v>0</v>
+      </c>
+      <c r="I57" s="8">
+        <v>0</v>
+      </c>
+      <c r="J57" s="8">
+        <v>0</v>
+      </c>
+      <c r="K57" s="8">
+        <v>0</v>
+      </c>
+      <c r="L57" s="8">
+        <v>0</v>
+      </c>
+      <c r="M57" s="8">
+        <v>0</v>
+      </c>
+      <c r="N57" s="8">
+        <v>0</v>
+      </c>
+      <c r="O57" s="8">
+        <v>0</v>
+      </c>
+      <c r="P57" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="8">
+        <v>0</v>
+      </c>
+      <c r="R57" s="8">
+        <v>0</v>
+      </c>
+      <c r="S57" s="8">
+        <v>0</v>
+      </c>
+      <c r="T57" s="8">
+        <v>0</v>
+      </c>
+      <c r="U57" s="8">
+        <v>0</v>
+      </c>
+      <c r="V57" s="8">
+        <v>0</v>
+      </c>
+      <c r="W57" s="5">
+        <v>0</v>
+      </c>
+      <c r="X57" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY57" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BG57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BH57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BJ57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BK57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BL57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BM57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BN57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BP57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BQ57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BR57" s="8">
+        <v>0</v>
+      </c>
+      <c r="BS57" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT57" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU57" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV57" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" s="5">
+        <v>0</v>
+      </c>
+      <c r="E58" s="5">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5">
+        <v>0</v>
+      </c>
+      <c r="H58" s="5">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5">
+        <v>0</v>
+      </c>
+      <c r="J58" s="5">
+        <v>0</v>
+      </c>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5">
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <v>0</v>
+      </c>
+      <c r="S58" s="5">
+        <v>0</v>
+      </c>
+      <c r="T58" s="5">
+        <v>0</v>
+      </c>
+      <c r="U58" s="5">
+        <v>0</v>
+      </c>
+      <c r="V58" s="5">
+        <v>0</v>
+      </c>
+      <c r="W58" s="5">
+        <v>0</v>
+      </c>
+      <c r="X58" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BC58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BD58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BE58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BF58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BG58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BI58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BJ58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BL58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BM58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BN58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BO58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BP58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BQ58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BR58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BS58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU58" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV58" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" s="8">
+        <v>0</v>
+      </c>
+      <c r="E59" s="8">
+        <v>0</v>
+      </c>
+      <c r="F59" s="8">
+        <v>0</v>
+      </c>
+      <c r="G59" s="8">
+        <v>0</v>
+      </c>
+      <c r="H59" s="8">
+        <v>0</v>
+      </c>
+      <c r="I59" s="8">
+        <v>0</v>
+      </c>
+      <c r="J59" s="8">
+        <v>0</v>
+      </c>
+      <c r="K59" s="8">
+        <v>0</v>
+      </c>
+      <c r="L59" s="8">
+        <v>0</v>
+      </c>
+      <c r="M59" s="8">
+        <v>0</v>
+      </c>
+      <c r="N59" s="8">
+        <v>0</v>
+      </c>
+      <c r="O59" s="8">
+        <v>0</v>
+      </c>
+      <c r="P59" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="8">
+        <v>0</v>
+      </c>
+      <c r="R59" s="8">
+        <v>0</v>
+      </c>
+      <c r="S59" s="8">
+        <v>0</v>
+      </c>
+      <c r="T59" s="8">
+        <v>0</v>
+      </c>
+      <c r="U59" s="8">
+        <v>0</v>
+      </c>
+      <c r="V59" s="8">
+        <v>0</v>
+      </c>
+      <c r="W59" s="5">
+        <v>0</v>
+      </c>
+      <c r="X59" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY59" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BG59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BH59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BJ59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BK59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BL59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BM59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BN59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BP59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BQ59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BR59" s="8">
+        <v>0</v>
+      </c>
+      <c r="BS59" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT59" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU59" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV59" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="D60" s="5">
+        <v>0</v>
+      </c>
+      <c r="E60" s="5">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5">
+        <v>0</v>
+      </c>
+      <c r="H60" s="5">
+        <v>0</v>
+      </c>
+      <c r="I60" s="5">
+        <v>0</v>
+      </c>
+      <c r="J60" s="5">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5">
+        <v>0</v>
+      </c>
+      <c r="M60" s="5">
+        <v>0</v>
+      </c>
+      <c r="N60" s="5">
+        <v>0</v>
+      </c>
+      <c r="O60" s="5">
+        <v>0</v>
+      </c>
+      <c r="P60" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="5">
+        <v>0</v>
+      </c>
+      <c r="R60" s="5">
+        <v>0</v>
+      </c>
+      <c r="S60" s="5">
+        <v>0</v>
+      </c>
+      <c r="T60" s="5">
+        <v>0</v>
+      </c>
+      <c r="U60" s="5">
+        <v>0</v>
+      </c>
+      <c r="V60" s="5">
+        <v>0</v>
+      </c>
+      <c r="W60" s="5">
+        <v>0</v>
+      </c>
+      <c r="X60" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BC60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BD60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BE60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BF60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BG60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BI60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BJ60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BL60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BM60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BN60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BO60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BP60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BQ60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BR60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BS60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU60" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV60" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D61" s="8">
+        <v>0</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0</v>
+      </c>
+      <c r="F61" s="8">
+        <v>0</v>
+      </c>
+      <c r="G61" s="8">
+        <v>0</v>
+      </c>
+      <c r="H61" s="8">
+        <v>0</v>
+      </c>
+      <c r="I61" s="8">
+        <v>0</v>
+      </c>
+      <c r="J61" s="8">
+        <v>0</v>
+      </c>
+      <c r="K61" s="8">
+        <v>0</v>
+      </c>
+      <c r="L61" s="8">
+        <v>0</v>
+      </c>
+      <c r="M61" s="8">
+        <v>0</v>
+      </c>
+      <c r="N61" s="8">
+        <v>0</v>
+      </c>
+      <c r="O61" s="8">
+        <v>0</v>
+      </c>
+      <c r="P61" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="8">
+        <v>0</v>
+      </c>
+      <c r="R61" s="8">
+        <v>0</v>
+      </c>
+      <c r="S61" s="8">
+        <v>0</v>
+      </c>
+      <c r="T61" s="8">
+        <v>0</v>
+      </c>
+      <c r="U61" s="8">
+        <v>0</v>
+      </c>
+      <c r="V61" s="8">
+        <v>0</v>
+      </c>
+      <c r="W61" s="5">
+        <v>0</v>
+      </c>
+      <c r="X61" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY61" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BG61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BH61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BJ61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BK61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BL61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BM61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BN61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BP61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BQ61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BR61" s="8">
+        <v>0</v>
+      </c>
+      <c r="BS61" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT61" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU61" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV61" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" s="5">
+        <v>0</v>
+      </c>
+      <c r="E62" s="5">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5">
+        <v>0</v>
+      </c>
+      <c r="H62" s="5">
+        <v>0</v>
+      </c>
+      <c r="I62" s="5">
+        <v>0</v>
+      </c>
+      <c r="J62" s="5">
+        <v>0</v>
+      </c>
+      <c r="K62" s="5">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5">
+        <v>0</v>
+      </c>
+      <c r="M62" s="5">
+        <v>0</v>
+      </c>
+      <c r="N62" s="5">
+        <v>0</v>
+      </c>
+      <c r="O62" s="5">
+        <v>0</v>
+      </c>
+      <c r="P62" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>0</v>
+      </c>
+      <c r="R62" s="5">
+        <v>0</v>
+      </c>
+      <c r="S62" s="5">
+        <v>0</v>
+      </c>
+      <c r="T62" s="5">
+        <v>0</v>
+      </c>
+      <c r="U62" s="5">
+        <v>0</v>
+      </c>
+      <c r="V62" s="5">
+        <v>0</v>
+      </c>
+      <c r="W62" s="5">
+        <v>0</v>
+      </c>
+      <c r="X62" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BC62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BD62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BE62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BF62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BG62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BI62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BJ62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BL62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BM62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BN62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BO62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BP62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BQ62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BR62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BS62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU62" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV62" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A63" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" s="8">
+        <v>0</v>
+      </c>
+      <c r="E63" s="8">
+        <v>0</v>
+      </c>
+      <c r="F63" s="8">
+        <v>0</v>
+      </c>
+      <c r="G63" s="8">
+        <v>0</v>
+      </c>
+      <c r="H63" s="8">
+        <v>0</v>
+      </c>
+      <c r="I63" s="8">
+        <v>0</v>
+      </c>
+      <c r="J63" s="8">
+        <v>0</v>
+      </c>
+      <c r="K63" s="8">
+        <v>0</v>
+      </c>
+      <c r="L63" s="8">
+        <v>0</v>
+      </c>
+      <c r="M63" s="8">
+        <v>0</v>
+      </c>
+      <c r="N63" s="8">
+        <v>0</v>
+      </c>
+      <c r="O63" s="8">
+        <v>0</v>
+      </c>
+      <c r="P63" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="8">
+        <v>0</v>
+      </c>
+      <c r="R63" s="8">
+        <v>0</v>
+      </c>
+      <c r="S63" s="8">
+        <v>0</v>
+      </c>
+      <c r="T63" s="8">
+        <v>0</v>
+      </c>
+      <c r="U63" s="8">
+        <v>0</v>
+      </c>
+      <c r="V63" s="8">
+        <v>0</v>
+      </c>
+      <c r="W63" s="5">
+        <v>0</v>
+      </c>
+      <c r="X63" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY63" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BG63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BH63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BJ63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BK63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BL63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BM63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BN63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BP63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BQ63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BR63" s="8">
+        <v>0</v>
+      </c>
+      <c r="BS63" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT63" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU63" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV63" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="5">
-        <v>0</v>
-      </c>
-      <c r="E54" s="5">
-        <v>0</v>
-      </c>
-      <c r="F54" s="5">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5">
-        <v>0</v>
-      </c>
-      <c r="H54" s="5">
-        <v>0</v>
-      </c>
-      <c r="I54" s="5">
-        <v>0</v>
-      </c>
-      <c r="J54" s="5">
-        <v>0</v>
-      </c>
-      <c r="K54" s="5">
-        <v>0</v>
-      </c>
-      <c r="L54" s="5">
-        <v>0</v>
-      </c>
-      <c r="M54" s="5">
-        <v>0</v>
-      </c>
-      <c r="N54" s="5">
-        <v>0</v>
-      </c>
-      <c r="O54" s="5">
-        <v>0</v>
-      </c>
-      <c r="P54" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="5">
-        <v>0</v>
-      </c>
-      <c r="R54" s="5">
-        <v>0</v>
-      </c>
-      <c r="S54" s="5">
-        <v>0</v>
-      </c>
-      <c r="T54" s="5">
-        <v>0</v>
-      </c>
-      <c r="U54" s="5">
-        <v>0</v>
-      </c>
-      <c r="V54" s="5">
-        <v>0</v>
-      </c>
-      <c r="W54" s="5">
-        <v>0</v>
-      </c>
-      <c r="X54" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AI54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AJ54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AK54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AL54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AW54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AY54" s="5">
-        <v>0</v>
-      </c>
-      <c r="AZ54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BA54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BB54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BC54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BD54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BE54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BF54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BG54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BH54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BI54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BJ54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BK54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BL54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU54" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV54" s="5">
+      <c r="D64" s="5">
+        <v>0</v>
+      </c>
+      <c r="E64" s="5">
+        <v>0</v>
+      </c>
+      <c r="F64" s="5">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5">
+        <v>0</v>
+      </c>
+      <c r="H64" s="5">
+        <v>0</v>
+      </c>
+      <c r="I64" s="5">
+        <v>0</v>
+      </c>
+      <c r="J64" s="5">
+        <v>0</v>
+      </c>
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5">
+        <v>0</v>
+      </c>
+      <c r="M64" s="5">
+        <v>0</v>
+      </c>
+      <c r="N64" s="5">
+        <v>0</v>
+      </c>
+      <c r="O64" s="5">
+        <v>0</v>
+      </c>
+      <c r="P64" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>0</v>
+      </c>
+      <c r="R64" s="5">
+        <v>0</v>
+      </c>
+      <c r="S64" s="5">
+        <v>0</v>
+      </c>
+      <c r="T64" s="5">
+        <v>0</v>
+      </c>
+      <c r="U64" s="5">
+        <v>0</v>
+      </c>
+      <c r="V64" s="5">
+        <v>0</v>
+      </c>
+      <c r="W64" s="5">
+        <v>0</v>
+      </c>
+      <c r="X64" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BC64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BD64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BE64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BF64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BG64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BI64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BJ64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BL64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BM64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BN64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BO64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BP64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BQ64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BR64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BS64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU64" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV64" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C55" s="6" t="s">
+    <row r="65" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A65" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D55" s="8">
-        <v>0</v>
-      </c>
-      <c r="E55" s="8">
-        <v>0</v>
-      </c>
-      <c r="F55" s="8">
-        <v>0</v>
-      </c>
-      <c r="G55" s="8">
-        <v>0</v>
-      </c>
-      <c r="H55" s="8">
-        <v>0</v>
-      </c>
-      <c r="I55" s="8">
-        <v>0</v>
-      </c>
-      <c r="J55" s="8">
-        <v>0</v>
-      </c>
-      <c r="K55" s="8">
-        <v>0</v>
-      </c>
-      <c r="L55" s="8">
-        <v>0</v>
-      </c>
-      <c r="M55" s="8">
-        <v>0</v>
-      </c>
-      <c r="N55" s="8">
-        <v>0</v>
-      </c>
-      <c r="O55" s="8">
-        <v>0</v>
-      </c>
-      <c r="P55" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="8">
-        <v>0</v>
-      </c>
-      <c r="R55" s="8">
-        <v>0</v>
-      </c>
-      <c r="S55" s="8">
-        <v>0</v>
-      </c>
-      <c r="T55" s="8">
-        <v>0</v>
-      </c>
-      <c r="U55" s="8">
-        <v>0</v>
-      </c>
-      <c r="V55" s="8">
-        <v>0</v>
-      </c>
-      <c r="W55" s="5">
-        <v>0</v>
-      </c>
-      <c r="X55" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y55" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AR55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AS55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AT55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AU55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AV55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AW55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AX55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AY55" s="8">
-        <v>0</v>
-      </c>
-      <c r="AZ55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BA55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BB55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BC55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BD55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BE55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BF55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BG55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BH55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BI55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BJ55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BK55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BL55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BM55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BN55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BO55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BP55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BQ55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BR55" s="8">
-        <v>0</v>
-      </c>
-      <c r="BS55" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT55" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU55" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV55" s="5">
+      <c r="D65" s="8">
+        <v>0</v>
+      </c>
+      <c r="E65" s="8">
+        <v>0</v>
+      </c>
+      <c r="F65" s="8">
+        <v>0</v>
+      </c>
+      <c r="G65" s="8">
+        <v>0</v>
+      </c>
+      <c r="H65" s="8">
+        <v>0</v>
+      </c>
+      <c r="I65" s="8">
+        <v>0</v>
+      </c>
+      <c r="J65" s="8">
+        <v>0</v>
+      </c>
+      <c r="K65" s="8">
+        <v>0</v>
+      </c>
+      <c r="L65" s="8">
+        <v>0</v>
+      </c>
+      <c r="M65" s="8">
+        <v>0</v>
+      </c>
+      <c r="N65" s="8">
+        <v>0</v>
+      </c>
+      <c r="O65" s="8">
+        <v>0</v>
+      </c>
+      <c r="P65" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="8">
+        <v>0</v>
+      </c>
+      <c r="R65" s="8">
+        <v>0</v>
+      </c>
+      <c r="S65" s="8">
+        <v>0</v>
+      </c>
+      <c r="T65" s="8">
+        <v>0</v>
+      </c>
+      <c r="U65" s="8">
+        <v>0</v>
+      </c>
+      <c r="V65" s="8">
+        <v>0</v>
+      </c>
+      <c r="W65" s="5">
+        <v>0</v>
+      </c>
+      <c r="X65" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY65" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BG65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BH65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BJ65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BK65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BL65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BM65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BN65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BP65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BQ65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BR65" s="8">
+        <v>0</v>
+      </c>
+      <c r="BS65" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT65" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU65" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV65" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="2" t="s">
+    <row r="66" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D56" s="5">
-        <v>0</v>
-      </c>
-      <c r="E56" s="5">
-        <v>0</v>
-      </c>
-      <c r="F56" s="5">
-        <v>0</v>
-      </c>
-      <c r="G56" s="5">
-        <v>0</v>
-      </c>
-      <c r="H56" s="5">
-        <v>0</v>
-      </c>
-      <c r="I56" s="5">
-        <v>0</v>
-      </c>
-      <c r="J56" s="5">
-        <v>0</v>
-      </c>
-      <c r="K56" s="5">
-        <v>0</v>
-      </c>
-      <c r="L56" s="5">
-        <v>0</v>
-      </c>
-      <c r="M56" s="5">
-        <v>0</v>
-      </c>
-      <c r="N56" s="5">
-        <v>0</v>
-      </c>
-      <c r="O56" s="5">
-        <v>0</v>
-      </c>
-      <c r="P56" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="5">
-        <v>0</v>
-      </c>
-      <c r="R56" s="5">
-        <v>0</v>
-      </c>
-      <c r="S56" s="5">
-        <v>0</v>
-      </c>
-      <c r="T56" s="5">
-        <v>0</v>
-      </c>
-      <c r="U56" s="5">
-        <v>0</v>
-      </c>
-      <c r="V56" s="5">
-        <v>0</v>
-      </c>
-      <c r="W56" s="5">
-        <v>0</v>
-      </c>
-      <c r="X56" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y56" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AI56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AJ56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AK56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AL56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AW56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AY56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AZ56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BA56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BB56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BC56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BD56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BE56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BF56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BG56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BH56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BI56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BJ56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BK56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BL56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU56" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV56" s="5">
+      <c r="D66" s="5">
+        <v>0</v>
+      </c>
+      <c r="E66" s="5">
+        <v>0</v>
+      </c>
+      <c r="F66" s="5">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5">
+        <v>0</v>
+      </c>
+      <c r="H66" s="5">
+        <v>0</v>
+      </c>
+      <c r="I66" s="5">
+        <v>0</v>
+      </c>
+      <c r="J66" s="5">
+        <v>0</v>
+      </c>
+      <c r="K66" s="5">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5">
+        <v>0</v>
+      </c>
+      <c r="M66" s="5">
+        <v>0</v>
+      </c>
+      <c r="N66" s="5">
+        <v>0</v>
+      </c>
+      <c r="O66" s="5">
+        <v>0</v>
+      </c>
+      <c r="P66" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="5">
+        <v>0</v>
+      </c>
+      <c r="R66" s="5">
+        <v>0</v>
+      </c>
+      <c r="S66" s="5">
+        <v>0</v>
+      </c>
+      <c r="T66" s="5">
+        <v>0</v>
+      </c>
+      <c r="U66" s="5">
+        <v>0</v>
+      </c>
+      <c r="V66" s="5">
+        <v>0</v>
+      </c>
+      <c r="W66" s="5">
+        <v>0</v>
+      </c>
+      <c r="X66" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BC66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BD66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BE66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BF66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BG66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BI66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BJ66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BL66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BM66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BN66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BO66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BP66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BQ66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BR66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BS66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU66" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV66" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C57" s="6" t="s">
+    <row r="67" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A67" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D57" s="8">
-        <v>0</v>
-      </c>
-      <c r="E57" s="8">
-        <v>0</v>
-      </c>
-      <c r="F57" s="8">
-        <v>0</v>
-      </c>
-      <c r="G57" s="8">
-        <v>0</v>
-      </c>
-      <c r="H57" s="8">
-        <v>0</v>
-      </c>
-      <c r="I57" s="8">
-        <v>0</v>
-      </c>
-      <c r="J57" s="8">
-        <v>0</v>
-      </c>
-      <c r="K57" s="8">
-        <v>0</v>
-      </c>
-      <c r="L57" s="8">
-        <v>0</v>
-      </c>
-      <c r="M57" s="8">
-        <v>0</v>
-      </c>
-      <c r="N57" s="8">
-        <v>0</v>
-      </c>
-      <c r="O57" s="8">
-        <v>0</v>
-      </c>
-      <c r="P57" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="8">
-        <v>0</v>
-      </c>
-      <c r="R57" s="8">
-        <v>0</v>
-      </c>
-      <c r="S57" s="8">
-        <v>0</v>
-      </c>
-      <c r="T57" s="8">
-        <v>0</v>
-      </c>
-      <c r="U57" s="8">
-        <v>0</v>
-      </c>
-      <c r="V57" s="8">
-        <v>0</v>
-      </c>
-      <c r="W57" s="5">
-        <v>0</v>
-      </c>
-      <c r="X57" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AR57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AS57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AT57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AU57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AV57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AW57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AX57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AY57" s="8">
-        <v>0</v>
-      </c>
-      <c r="AZ57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BA57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BB57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BC57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BD57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BE57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BF57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BG57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BH57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BI57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BJ57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BK57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BL57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BM57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BN57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BO57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BP57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BQ57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BR57" s="8">
-        <v>0</v>
-      </c>
-      <c r="BS57" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT57" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU57" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV57" s="5">
+      <c r="D67" s="8">
+        <v>0</v>
+      </c>
+      <c r="E67" s="8">
+        <v>0</v>
+      </c>
+      <c r="F67" s="8">
+        <v>0</v>
+      </c>
+      <c r="G67" s="8">
+        <v>0</v>
+      </c>
+      <c r="H67" s="8">
+        <v>0</v>
+      </c>
+      <c r="I67" s="8">
+        <v>0</v>
+      </c>
+      <c r="J67" s="8">
+        <v>0</v>
+      </c>
+      <c r="K67" s="8">
+        <v>0</v>
+      </c>
+      <c r="L67" s="8">
+        <v>0</v>
+      </c>
+      <c r="M67" s="8">
+        <v>0</v>
+      </c>
+      <c r="N67" s="8">
+        <v>0</v>
+      </c>
+      <c r="O67" s="8">
+        <v>0</v>
+      </c>
+      <c r="P67" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="8">
+        <v>0</v>
+      </c>
+      <c r="R67" s="8">
+        <v>0</v>
+      </c>
+      <c r="S67" s="8">
+        <v>0</v>
+      </c>
+      <c r="T67" s="8">
+        <v>0</v>
+      </c>
+      <c r="U67" s="8">
+        <v>0</v>
+      </c>
+      <c r="V67" s="8">
+        <v>0</v>
+      </c>
+      <c r="W67" s="5">
+        <v>0</v>
+      </c>
+      <c r="X67" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY67" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BG67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BH67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BJ67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BK67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BL67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BM67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BN67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BP67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BQ67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BR67" s="8">
+        <v>0</v>
+      </c>
+      <c r="BS67" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT67" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU67" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV67" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C58" s="2" t="s">
+    <row r="68" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D58" s="5">
-        <v>0</v>
-      </c>
-      <c r="E58" s="5">
-        <v>0</v>
-      </c>
-      <c r="F58" s="5">
-        <v>0</v>
-      </c>
-      <c r="G58" s="5">
-        <v>0</v>
-      </c>
-      <c r="H58" s="5">
-        <v>0</v>
-      </c>
-      <c r="I58" s="5">
-        <v>0</v>
-      </c>
-      <c r="J58" s="5">
-        <v>0</v>
-      </c>
-      <c r="K58" s="5">
-        <v>0</v>
-      </c>
-      <c r="L58" s="5">
-        <v>0</v>
-      </c>
-      <c r="M58" s="5">
-        <v>0</v>
-      </c>
-      <c r="N58" s="5">
-        <v>0</v>
-      </c>
-      <c r="O58" s="5">
-        <v>0</v>
-      </c>
-      <c r="P58" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="5">
-        <v>0</v>
-      </c>
-      <c r="R58" s="5">
-        <v>0</v>
-      </c>
-      <c r="S58" s="5">
-        <v>0</v>
-      </c>
-      <c r="T58" s="5">
-        <v>0</v>
-      </c>
-      <c r="U58" s="5">
-        <v>0</v>
-      </c>
-      <c r="V58" s="5">
-        <v>0</v>
-      </c>
-      <c r="W58" s="5">
-        <v>0</v>
-      </c>
-      <c r="X58" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AI58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AJ58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AK58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AL58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AW58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AY58" s="5">
-        <v>0</v>
-      </c>
-      <c r="AZ58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BA58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BB58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BC58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BD58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BE58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BF58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BG58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BH58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BI58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BJ58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BK58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BL58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU58" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV58" s="5">
+      <c r="D68" s="5">
+        <v>0</v>
+      </c>
+      <c r="E68" s="5">
+        <v>0</v>
+      </c>
+      <c r="F68" s="5">
+        <v>0</v>
+      </c>
+      <c r="G68" s="5">
+        <v>0</v>
+      </c>
+      <c r="H68" s="5">
+        <v>0</v>
+      </c>
+      <c r="I68" s="5">
+        <v>0</v>
+      </c>
+      <c r="J68" s="5">
+        <v>0</v>
+      </c>
+      <c r="K68" s="5">
+        <v>0</v>
+      </c>
+      <c r="L68" s="5">
+        <v>0</v>
+      </c>
+      <c r="M68" s="5">
+        <v>0</v>
+      </c>
+      <c r="N68" s="5">
+        <v>0</v>
+      </c>
+      <c r="O68" s="5">
+        <v>0</v>
+      </c>
+      <c r="P68" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>0</v>
+      </c>
+      <c r="R68" s="5">
+        <v>0</v>
+      </c>
+      <c r="S68" s="5">
+        <v>0</v>
+      </c>
+      <c r="T68" s="5">
+        <v>0</v>
+      </c>
+      <c r="U68" s="5">
+        <v>0</v>
+      </c>
+      <c r="V68" s="5">
+        <v>0</v>
+      </c>
+      <c r="W68" s="5">
+        <v>0</v>
+      </c>
+      <c r="X68" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BC68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BD68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BE68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BF68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BG68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BI68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BJ68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BL68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BM68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BN68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BO68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BP68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BQ68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BR68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BS68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU68" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV68" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D59" s="8">
-        <v>0</v>
-      </c>
-      <c r="E59" s="8">
-        <v>0</v>
-      </c>
-      <c r="F59" s="8">
-        <v>0</v>
-      </c>
-      <c r="G59" s="8">
-        <v>0</v>
-      </c>
-      <c r="H59" s="8">
-        <v>0</v>
-      </c>
-      <c r="I59" s="8">
-        <v>0</v>
-      </c>
-      <c r="J59" s="8">
-        <v>0</v>
-      </c>
-      <c r="K59" s="8">
-        <v>0</v>
-      </c>
-      <c r="L59" s="8">
-        <v>0</v>
-      </c>
-      <c r="M59" s="8">
-        <v>0</v>
-      </c>
-      <c r="N59" s="8">
-        <v>0</v>
-      </c>
-      <c r="O59" s="8">
-        <v>0</v>
-      </c>
-      <c r="P59" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="8">
-        <v>0</v>
-      </c>
-      <c r="R59" s="8">
-        <v>0</v>
-      </c>
-      <c r="S59" s="8">
-        <v>0</v>
-      </c>
-      <c r="T59" s="8">
-        <v>0</v>
-      </c>
-      <c r="U59" s="8">
-        <v>0</v>
-      </c>
-      <c r="V59" s="8">
-        <v>0</v>
-      </c>
-      <c r="W59" s="5">
-        <v>0</v>
-      </c>
-      <c r="X59" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AR59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AS59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AT59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AU59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AV59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AW59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AX59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AY59" s="8">
-        <v>0</v>
-      </c>
-      <c r="AZ59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BA59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BB59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BC59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BD59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BE59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BF59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BG59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BH59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BI59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BJ59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BK59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BL59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BM59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BN59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BO59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BP59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BQ59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BR59" s="8">
-        <v>0</v>
-      </c>
-      <c r="BS59" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT59" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU59" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV59" s="5">
+    <row r="69" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A69" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D69" s="8">
+        <v>0</v>
+      </c>
+      <c r="E69" s="8">
+        <v>0</v>
+      </c>
+      <c r="F69" s="8">
+        <v>0</v>
+      </c>
+      <c r="G69" s="8">
+        <v>0</v>
+      </c>
+      <c r="H69" s="8">
+        <v>0</v>
+      </c>
+      <c r="I69" s="8">
+        <v>0</v>
+      </c>
+      <c r="J69" s="8">
+        <v>0</v>
+      </c>
+      <c r="K69" s="8">
+        <v>0</v>
+      </c>
+      <c r="L69" s="8">
+        <v>0</v>
+      </c>
+      <c r="M69" s="8">
+        <v>0</v>
+      </c>
+      <c r="N69" s="8">
+        <v>0</v>
+      </c>
+      <c r="O69" s="8">
+        <v>0</v>
+      </c>
+      <c r="P69" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="8">
+        <v>0</v>
+      </c>
+      <c r="R69" s="8">
+        <v>0</v>
+      </c>
+      <c r="S69" s="8">
+        <v>0</v>
+      </c>
+      <c r="T69" s="8">
+        <v>0</v>
+      </c>
+      <c r="U69" s="8">
+        <v>0</v>
+      </c>
+      <c r="V69" s="8">
+        <v>0</v>
+      </c>
+      <c r="W69" s="5">
+        <v>0</v>
+      </c>
+      <c r="X69" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BF69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BG69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BH69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BJ69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BK69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BL69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BM69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BN69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BP69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BQ69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BR69" s="8">
+        <v>0</v>
+      </c>
+      <c r="BS69" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT69" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU69" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV69" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C60" s="2" t="s">
+    <row r="70" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D60" s="5">
-        <v>0</v>
-      </c>
-      <c r="E60" s="5">
-        <v>0</v>
-      </c>
-      <c r="F60" s="5">
-        <v>0</v>
-      </c>
-      <c r="G60" s="5">
-        <v>0</v>
-      </c>
-      <c r="H60" s="5">
-        <v>0</v>
-      </c>
-      <c r="I60" s="5">
-        <v>0</v>
-      </c>
-      <c r="J60" s="5">
-        <v>0</v>
-      </c>
-      <c r="K60" s="5">
-        <v>0</v>
-      </c>
-      <c r="L60" s="5">
-        <v>0</v>
-      </c>
-      <c r="M60" s="5">
-        <v>0</v>
-      </c>
-      <c r="N60" s="5">
-        <v>0</v>
-      </c>
-      <c r="O60" s="5">
-        <v>0</v>
-      </c>
-      <c r="P60" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="5">
-        <v>0</v>
-      </c>
-      <c r="R60" s="5">
-        <v>0</v>
-      </c>
-      <c r="S60" s="5">
-        <v>0</v>
-      </c>
-      <c r="T60" s="5">
-        <v>0</v>
-      </c>
-      <c r="U60" s="5">
-        <v>0</v>
-      </c>
-      <c r="V60" s="5">
-        <v>0</v>
-      </c>
-      <c r="W60" s="5">
-        <v>0</v>
-      </c>
-      <c r="X60" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AI60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AJ60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AK60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AL60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AW60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AY60" s="5">
-        <v>0</v>
-      </c>
-      <c r="AZ60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BA60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BB60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BC60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BD60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BE60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BF60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BG60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BH60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BI60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BJ60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BK60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BL60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU60" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV60" s="5">
+      <c r="D70" s="5">
+        <v>0</v>
+      </c>
+      <c r="E70" s="5">
+        <v>0</v>
+      </c>
+      <c r="F70" s="5">
+        <v>0</v>
+      </c>
+      <c r="G70" s="5">
+        <v>0</v>
+      </c>
+      <c r="H70" s="5">
+        <v>0</v>
+      </c>
+      <c r="I70" s="5">
+        <v>0</v>
+      </c>
+      <c r="J70" s="5">
+        <v>0</v>
+      </c>
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5">
+        <v>0</v>
+      </c>
+      <c r="M70" s="5">
+        <v>0</v>
+      </c>
+      <c r="N70" s="5">
+        <v>0</v>
+      </c>
+      <c r="O70" s="5">
+        <v>0</v>
+      </c>
+      <c r="P70" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="5">
+        <v>0</v>
+      </c>
+      <c r="R70" s="5">
+        <v>0</v>
+      </c>
+      <c r="S70" s="5">
+        <v>0</v>
+      </c>
+      <c r="T70" s="5">
+        <v>0</v>
+      </c>
+      <c r="U70" s="5">
+        <v>0</v>
+      </c>
+      <c r="V70" s="5">
+        <v>0</v>
+      </c>
+      <c r="W70" s="5">
+        <v>0</v>
+      </c>
+      <c r="X70" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BC70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BD70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BE70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BF70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BG70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BI70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BJ70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BL70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BM70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BN70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BO70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BP70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BQ70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BR70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BS70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BT70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BU70" s="5">
+        <v>0</v>
+      </c>
+      <c r="BV70" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C61" s="6" t="s">
+    <row r="71" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A71" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="D61" s="8">
-        <v>0</v>
-      </c>
-      <c r="E61" s="8">
-        <v>0</v>
-      </c>
-      <c r="F61" s="8">
-        <v>0</v>
-      </c>
-      <c r="G61" s="8">
-        <v>0</v>
-      </c>
-      <c r="H61" s="8">
-        <v>0</v>
-      </c>
-      <c r="I61" s="8">
-        <v>0</v>
-      </c>
-      <c r="J61" s="8">
-        <v>0</v>
-      </c>
-      <c r="K61" s="8">
-        <v>0</v>
-      </c>
-      <c r="L61" s="8">
-        <v>0</v>
-      </c>
-      <c r="M61" s="8">
-        <v>0</v>
-      </c>
-      <c r="N61" s="8">
-        <v>0</v>
-      </c>
-      <c r="O61" s="8">
-        <v>0</v>
-      </c>
-      <c r="P61" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="8">
-        <v>0</v>
-      </c>
-      <c r="R61" s="8">
-        <v>0</v>
-      </c>
-      <c r="S61" s="8">
-        <v>0</v>
-      </c>
-      <c r="T61" s="8">
-        <v>0</v>
-      </c>
-      <c r="U61" s="8">
-        <v>0</v>
-      </c>
-      <c r="V61" s="8">
-        <v>0</v>
-      </c>
-      <c r="W61" s="5">
-        <v>0</v>
-      </c>
-      <c r="X61" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AR61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AS61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AT61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AU61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AV61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AW61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AX61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AY61" s="8">
-        <v>0</v>
-      </c>
-      <c r="AZ61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BA61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BB61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BC61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BD61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BE61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BF61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BG61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BH61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BI61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BJ61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BK61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BL61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BM61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BN61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BO61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BP61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BQ61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BR61" s="8">
-        <v>0</v>
-      </c>
-      <c r="BS61" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT61" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU61" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV61" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D62" s="5">
-        <v>0</v>
-      </c>
-      <c r="E62" s="5">
-        <v>0</v>
-      </c>
-      <c r="F62" s="5">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5">
-        <v>0</v>
-      </c>
-      <c r="H62" s="5">
-        <v>0</v>
-      </c>
-      <c r="I62" s="5">
-        <v>0</v>
-      </c>
-      <c r="J62" s="5">
-        <v>0</v>
-      </c>
-      <c r="K62" s="5">
-        <v>0</v>
-      </c>
-      <c r="L62" s="5">
-        <v>0</v>
-      </c>
-      <c r="M62" s="5">
-        <v>0</v>
-      </c>
-      <c r="N62" s="5">
-        <v>0</v>
-      </c>
-      <c r="O62" s="5">
-        <v>0</v>
-      </c>
-      <c r="P62" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="5">
-        <v>0</v>
-      </c>
-      <c r="R62" s="5">
-        <v>0</v>
-      </c>
-      <c r="S62" s="5">
-        <v>0</v>
-      </c>
-      <c r="T62" s="5">
-        <v>0</v>
-      </c>
-      <c r="U62" s="5">
-        <v>0</v>
-      </c>
-      <c r="V62" s="5">
-        <v>0</v>
-      </c>
-      <c r="W62" s="5">
-        <v>0</v>
-      </c>
-      <c r="X62" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AI62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AJ62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AK62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AL62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AW62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AY62" s="5">
-        <v>0</v>
-      </c>
-      <c r="AZ62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BA62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BB62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BC62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BD62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BE62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BF62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BG62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BH62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BI62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BJ62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BK62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BL62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU62" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV62" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D63" s="8">
-        <v>0</v>
-      </c>
-      <c r="E63" s="8">
-        <v>0</v>
-      </c>
-      <c r="F63" s="8">
-        <v>0</v>
-      </c>
-      <c r="G63" s="8">
-        <v>0</v>
-      </c>
-      <c r="H63" s="8">
-        <v>0</v>
-      </c>
-      <c r="I63" s="8">
-        <v>0</v>
-      </c>
-      <c r="J63" s="8">
-        <v>0</v>
-      </c>
-      <c r="K63" s="8">
-        <v>0</v>
-      </c>
-      <c r="L63" s="8">
-        <v>0</v>
-      </c>
-      <c r="M63" s="8">
-        <v>0</v>
-      </c>
-      <c r="N63" s="8">
-        <v>0</v>
-      </c>
-      <c r="O63" s="8">
-        <v>0</v>
-      </c>
-      <c r="P63" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="8">
-        <v>0</v>
-      </c>
-      <c r="R63" s="8">
-        <v>0</v>
-      </c>
-      <c r="S63" s="8">
-        <v>0</v>
-      </c>
-      <c r="T63" s="8">
-        <v>0</v>
-      </c>
-      <c r="U63" s="8">
-        <v>0</v>
-      </c>
-      <c r="V63" s="8">
-        <v>0</v>
-      </c>
-      <c r="W63" s="5">
-        <v>0</v>
-      </c>
-      <c r="X63" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y63" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AR63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AS63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AT63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AU63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AV63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AW63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AX63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AY63" s="8">
-        <v>0</v>
-      </c>
-      <c r="AZ63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BA63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BB63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BC63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BD63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BE63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BF63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BG63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BH63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BI63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BJ63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BK63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BL63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BM63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BN63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BO63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BP63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BQ63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BR63" s="8">
-        <v>0</v>
-      </c>
-      <c r="BS63" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT63" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU63" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV63" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D64" s="5">
-        <v>0</v>
-      </c>
-      <c r="E64" s="5">
-        <v>0</v>
-      </c>
-      <c r="F64" s="5">
-        <v>0</v>
-      </c>
-      <c r="G64" s="5">
-        <v>0</v>
-      </c>
-      <c r="H64" s="5">
-        <v>0</v>
-      </c>
-      <c r="I64" s="5">
-        <v>0</v>
-      </c>
-      <c r="J64" s="5">
-        <v>0</v>
-      </c>
-      <c r="K64" s="5">
-        <v>0</v>
-      </c>
-      <c r="L64" s="5">
-        <v>0</v>
-      </c>
-      <c r="M64" s="5">
-        <v>0</v>
-      </c>
-      <c r="N64" s="5">
-        <v>0</v>
-      </c>
-      <c r="O64" s="5">
-        <v>0</v>
-      </c>
-      <c r="P64" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="5">
-        <v>0</v>
-      </c>
-      <c r="R64" s="5">
-        <v>0</v>
-      </c>
-      <c r="S64" s="5">
-        <v>0</v>
-      </c>
-      <c r="T64" s="5">
-        <v>0</v>
-      </c>
-      <c r="U64" s="5">
-        <v>0</v>
-      </c>
-      <c r="V64" s="5">
-        <v>0</v>
-      </c>
-      <c r="W64" s="5">
-        <v>0</v>
-      </c>
-      <c r="X64" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y64" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AI64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AJ64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AK64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AL64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AW64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AY64" s="5">
-        <v>0</v>
-      </c>
-      <c r="AZ64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BA64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BB64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BC64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BD64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BE64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BF64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BG64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BH64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BI64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BJ64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BK64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BL64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU64" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV64" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D65" s="8">
-        <v>0</v>
-      </c>
-      <c r="E65" s="8">
-        <v>0</v>
-      </c>
-      <c r="F65" s="8">
-        <v>0</v>
-      </c>
-      <c r="G65" s="8">
-        <v>0</v>
-      </c>
-      <c r="H65" s="8">
-        <v>0</v>
-      </c>
-      <c r="I65" s="8">
-        <v>0</v>
-      </c>
-      <c r="J65" s="8">
-        <v>0</v>
-      </c>
-      <c r="K65" s="8">
-        <v>0</v>
-      </c>
-      <c r="L65" s="8">
-        <v>0</v>
-      </c>
-      <c r="M65" s="8">
-        <v>0</v>
-      </c>
-      <c r="N65" s="8">
-        <v>0</v>
-      </c>
-      <c r="O65" s="8">
-        <v>0</v>
-      </c>
-      <c r="P65" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="8">
-        <v>0</v>
-      </c>
-      <c r="R65" s="8">
-        <v>0</v>
-      </c>
-      <c r="S65" s="8">
-        <v>0</v>
-      </c>
-      <c r="T65" s="8">
-        <v>0</v>
-      </c>
-      <c r="U65" s="8">
-        <v>0</v>
-      </c>
-      <c r="V65" s="8">
-        <v>0</v>
-      </c>
-      <c r="W65" s="5">
-        <v>0</v>
-      </c>
-      <c r="X65" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y65" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AR65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AS65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AT65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AU65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AV65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AW65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AX65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AY65" s="8">
-        <v>0</v>
-      </c>
-      <c r="AZ65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BA65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BB65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BC65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BD65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BE65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BF65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BG65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BH65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BI65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BJ65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BK65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BL65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BM65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BN65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BO65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BP65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BQ65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BR65" s="8">
-        <v>0</v>
-      </c>
-      <c r="BS65" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT65" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU65" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV65" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D66" s="5">
-        <v>0</v>
-      </c>
-      <c r="E66" s="5">
-        <v>0</v>
-      </c>
-      <c r="F66" s="5">
-        <v>0</v>
-      </c>
-      <c r="G66" s="5">
-        <v>0</v>
-      </c>
-      <c r="H66" s="5">
-        <v>0</v>
-      </c>
-      <c r="I66" s="5">
-        <v>0</v>
-      </c>
-      <c r="J66" s="5">
-        <v>0</v>
-      </c>
-      <c r="K66" s="5">
-        <v>0</v>
-      </c>
-      <c r="L66" s="5">
-        <v>0</v>
-      </c>
-      <c r="M66" s="5">
-        <v>0</v>
-      </c>
-      <c r="N66" s="5">
-        <v>0</v>
-      </c>
-      <c r="O66" s="5">
-        <v>0</v>
-      </c>
-      <c r="P66" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="5">
-        <v>0</v>
-      </c>
-      <c r="R66" s="5">
-        <v>0</v>
-      </c>
-      <c r="S66" s="5">
-        <v>0</v>
-      </c>
-      <c r="T66" s="5">
-        <v>0</v>
-      </c>
-      <c r="U66" s="5">
-        <v>0</v>
-      </c>
-      <c r="V66" s="5">
-        <v>0</v>
-      </c>
-      <c r="W66" s="5">
-        <v>0</v>
-      </c>
-      <c r="X66" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AI66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AJ66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AK66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AL66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AW66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AY66" s="5">
-        <v>0</v>
-      </c>
-      <c r="AZ66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BA66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BB66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BC66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BD66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BE66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BF66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BG66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BH66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BI66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BJ66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BK66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BL66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU66" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV66" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D67" s="8">
-        <v>0</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0</v>
-      </c>
-      <c r="F67" s="8">
-        <v>0</v>
-      </c>
-      <c r="G67" s="8">
-        <v>0</v>
-      </c>
-      <c r="H67" s="8">
-        <v>0</v>
-      </c>
-      <c r="I67" s="8">
-        <v>0</v>
-      </c>
-      <c r="J67" s="8">
-        <v>0</v>
-      </c>
-      <c r="K67" s="8">
-        <v>0</v>
-      </c>
-      <c r="L67" s="8">
-        <v>0</v>
-      </c>
-      <c r="M67" s="8">
-        <v>0</v>
-      </c>
-      <c r="N67" s="8">
-        <v>0</v>
-      </c>
-      <c r="O67" s="8">
-        <v>0</v>
-      </c>
-      <c r="P67" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="8">
-        <v>0</v>
-      </c>
-      <c r="R67" s="8">
-        <v>0</v>
-      </c>
-      <c r="S67" s="8">
-        <v>0</v>
-      </c>
-      <c r="T67" s="8">
-        <v>0</v>
-      </c>
-      <c r="U67" s="8">
-        <v>0</v>
-      </c>
-      <c r="V67" s="8">
-        <v>0</v>
-      </c>
-      <c r="W67" s="5">
-        <v>0</v>
-      </c>
-      <c r="X67" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y67" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AR67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AS67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AT67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AU67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AV67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AW67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AX67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AY67" s="8">
-        <v>0</v>
-      </c>
-      <c r="AZ67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BA67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BB67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BC67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BD67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BE67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BF67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BG67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BH67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BI67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BJ67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BK67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BL67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BM67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BN67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BO67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BP67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BQ67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BR67" s="8">
-        <v>0</v>
-      </c>
-      <c r="BS67" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT67" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU67" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV67" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D68" s="5">
-        <v>0</v>
-      </c>
-      <c r="E68" s="5">
-        <v>0</v>
-      </c>
-      <c r="F68" s="5">
-        <v>0</v>
-      </c>
-      <c r="G68" s="5">
-        <v>0</v>
-      </c>
-      <c r="H68" s="5">
-        <v>0</v>
-      </c>
-      <c r="I68" s="5">
-        <v>0</v>
-      </c>
-      <c r="J68" s="5">
-        <v>0</v>
-      </c>
-      <c r="K68" s="5">
-        <v>0</v>
-      </c>
-      <c r="L68" s="5">
-        <v>0</v>
-      </c>
-      <c r="M68" s="5">
-        <v>0</v>
-      </c>
-      <c r="N68" s="5">
-        <v>0</v>
-      </c>
-      <c r="O68" s="5">
-        <v>0</v>
-      </c>
-      <c r="P68" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="5">
-        <v>0</v>
-      </c>
-      <c r="R68" s="5">
-        <v>0</v>
-      </c>
-      <c r="S68" s="5">
-        <v>0</v>
-      </c>
-      <c r="T68" s="5">
-        <v>0</v>
-      </c>
-      <c r="U68" s="5">
-        <v>0</v>
-      </c>
-      <c r="V68" s="5">
-        <v>0</v>
-      </c>
-      <c r="W68" s="5">
-        <v>0</v>
-      </c>
-      <c r="X68" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y68" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AI68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AJ68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AK68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AL68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AW68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AY68" s="5">
-        <v>0</v>
-      </c>
-      <c r="AZ68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BA68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BB68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BC68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BD68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BE68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BF68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BG68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BH68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BI68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BJ68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BK68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BL68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU68" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV68" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D69" s="8">
-        <v>0</v>
-      </c>
-      <c r="E69" s="8">
-        <v>0</v>
-      </c>
-      <c r="F69" s="8">
-        <v>0</v>
-      </c>
-      <c r="G69" s="8">
-        <v>0</v>
-      </c>
-      <c r="H69" s="8">
-        <v>0</v>
-      </c>
-      <c r="I69" s="8">
-        <v>0</v>
-      </c>
-      <c r="J69" s="8">
-        <v>0</v>
-      </c>
-      <c r="K69" s="8">
-        <v>0</v>
-      </c>
-      <c r="L69" s="8">
-        <v>0</v>
-      </c>
-      <c r="M69" s="8">
-        <v>0</v>
-      </c>
-      <c r="N69" s="8">
-        <v>0</v>
-      </c>
-      <c r="O69" s="8">
-        <v>0</v>
-      </c>
-      <c r="P69" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="8">
-        <v>0</v>
-      </c>
-      <c r="R69" s="8">
-        <v>0</v>
-      </c>
-      <c r="S69" s="8">
-        <v>0</v>
-      </c>
-      <c r="T69" s="8">
-        <v>0</v>
-      </c>
-      <c r="U69" s="8">
-        <v>0</v>
-      </c>
-      <c r="V69" s="8">
-        <v>0</v>
-      </c>
-      <c r="W69" s="5">
-        <v>0</v>
-      </c>
-      <c r="X69" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y69" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AR69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AS69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AT69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AU69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AV69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AW69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AX69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AY69" s="8">
-        <v>0</v>
-      </c>
-      <c r="AZ69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BA69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BB69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BC69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BD69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BE69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BF69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BG69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BH69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BI69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BJ69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BK69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BL69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BM69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BN69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BO69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BP69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BQ69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BR69" s="8">
-        <v>0</v>
-      </c>
-      <c r="BS69" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT69" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU69" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV69" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D70" s="5">
-        <v>0</v>
-      </c>
-      <c r="E70" s="5">
-        <v>0</v>
-      </c>
-      <c r="F70" s="5">
-        <v>0</v>
-      </c>
-      <c r="G70" s="5">
-        <v>0</v>
-      </c>
-      <c r="H70" s="5">
-        <v>0</v>
-      </c>
-      <c r="I70" s="5">
-        <v>0</v>
-      </c>
-      <c r="J70" s="5">
-        <v>0</v>
-      </c>
-      <c r="K70" s="5">
-        <v>0</v>
-      </c>
-      <c r="L70" s="5">
-        <v>0</v>
-      </c>
-      <c r="M70" s="5">
-        <v>0</v>
-      </c>
-      <c r="N70" s="5">
-        <v>0</v>
-      </c>
-      <c r="O70" s="5">
-        <v>0</v>
-      </c>
-      <c r="P70" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="5">
-        <v>0</v>
-      </c>
-      <c r="R70" s="5">
-        <v>0</v>
-      </c>
-      <c r="S70" s="5">
-        <v>0</v>
-      </c>
-      <c r="T70" s="5">
-        <v>0</v>
-      </c>
-      <c r="U70" s="5">
-        <v>0</v>
-      </c>
-      <c r="V70" s="5">
-        <v>0</v>
-      </c>
-      <c r="W70" s="5">
-        <v>0</v>
-      </c>
-      <c r="X70" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y70" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AG70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AI70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AJ70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AK70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AL70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AW70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AY70" s="5">
-        <v>0</v>
-      </c>
-      <c r="AZ70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BA70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BB70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BC70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BD70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BE70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BF70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BG70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BH70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BI70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BJ70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BK70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BL70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU70" s="5">
-        <v>0</v>
-      </c>
-      <c r="BV70" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="D71" s="8">
         <v>0</v>
@@ -16587,13 +16587,13 @@
     </row>
     <row r="72" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D72" s="8">
         <v>0</v>
@@ -16811,13 +16811,13 @@
     </row>
     <row r="73" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D73" s="8">
         <v>0</v>

--- a/orecraft_database.xlsx
+++ b/orecraft_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDDF852-D379-46B6-8A4C-ACC35E7FA4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489D671C-C708-469B-983F-D90DED906B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7196,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="BM29" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BN29" s="5">
         <v>0</v>

--- a/orecraft_database.xlsx
+++ b/orecraft_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489D671C-C708-469B-983F-D90DED906B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048CE991-BAEA-4374-9182-E6C09BAC8263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7196,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="BM29" s="5">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BN29" s="5">
         <v>0</v>
